--- a/artfynd/A 59875-2025 artfynd.xlsx
+++ b/artfynd/A 59875-2025 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130792821</v>
+        <v>130792813</v>
       </c>
       <c r="B2" t="n">
-        <v>58564</v>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -789,27 +789,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130792813</v>
+        <v>130792839</v>
       </c>
       <c r="B3" t="n">
-        <v>57805</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130792816</v>
+        <v>130792800</v>
       </c>
       <c r="B4" t="n">
-        <v>58041</v>
+        <v>58393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>102999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1017,32 +1017,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130792800</v>
+        <v>130792828</v>
       </c>
       <c r="B5" t="n">
-        <v>58321</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102999</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1131,27 +1131,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130792828</v>
+        <v>130792816</v>
       </c>
       <c r="B6" t="n">
-        <v>58256</v>
+        <v>58112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1245,27 +1245,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130792839</v>
+        <v>130792821</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>58636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">

--- a/artfynd/A 59875-2025 artfynd.xlsx
+++ b/artfynd/A 59875-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792813</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792839</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792800</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792828</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792816</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1356,8 +1386,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130792821</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>